--- a/reports/Дашборд.xlsx
+++ b/reports/Дашборд.xlsx
@@ -207,10 +207,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1181,7 +1181,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Источник: Google Таблица (обновлено 07.10.2026 13:14)  ·  Сформировано: 07.10.2026 13:14  ·  Обновить: двойной клик по файлу «Обновить_дашборд.bat»</t>
+          <t>Источник: Google Таблица (обновлено 07.10.2026 14:01)  ·  Сформировано: 07.10.2026 14:01  ·  Обновить: двойной клик по файлу «Запустить.bat»</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -11073,7 +11073,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>КАК ОБНОВИТЬ ДАШБОРД</t>
+          <t>КАК ПОЛЬЗОВАТЬСЯ: ОДИН ЗАПУСК</t>
         </is>
       </c>
     </row>
@@ -11083,7 +11083,7 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>1. Откройте Google Таблицу и поправьте данные: статусы монет, сделки, клиентов.</t>
+          <t>1. Поправьте данные в Google Таблице: статусы монет, сделки, клиентов.</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>2. Дважды кликните файл «Обновить_дашборд.bat» в папке проекта.</t>
+          <t>2. Дважды кликните файл «Запустить.bat» в папке проекта — он обновит всё сам.</t>
         </is>
       </c>
     </row>
@@ -11103,98 +11103,139 @@
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="16" t="inlineStr">
         <is>
-          <t>3. Откройте файл reports\Дашборд.xlsx — он пересобран по свежим данным.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="8" customHeight="1">
-      <c r="A8" s="17" t="inlineStr"/>
+          <t>3. Откроется файл «Рекомендации_для_вставки.xlsx» → вкладка «Копировать»:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   клик на A1 → Ctrl+A → Ctrl+C, затем Google Таблица → вкладка</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>ЧТО ГДЕ СМОТРЕТЬ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Дашборд» — карточки показателей, топ-5 рекомендаций для каждого клиента, графики.</t>
-        </is>
-      </c>
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   «Рекомендации» → первая пустая строка → Ctrl+V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1">
+      <c r="A10" s="17" t="inlineStr"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • «Рекомендации» — полный список монет с обоснованием каждой.</t>
+          <t>4. Этот дашборд (reports\Дашборд.xlsx) открывается тем же запуском: карточки,</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • «Профили клиентов» — кто что коллекционирует и какой бюджетный коридор.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Каталог монет» — все монеты; у доступных указана оценка цены по аналогам.</t>
-        </is>
-      </c>
+          <t xml:space="preserve">   графики и обоснование каждой рекомендации.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="8" customHeight="1">
+      <c r="A13" s="17" t="inlineStr"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Качество данных» — 30 автоматических проверок; строки FAIL надо закрыть.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • «Метрики» — насколько точно система угадывала реальные покупки на истории.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="8" customHeight="1">
-      <c r="A16" s="17" t="inlineStr"/>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Колонки «за сколько» и «предложено» система не трогает: их заполняете вы, как и прежде.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1">
+      <c r="A15" s="17" t="inlineStr"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>ЧТО ГДЕ СМОТРЕТЬ</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>ЕСЛИ ЧТО-ТО НЕ ТАК</t>
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • «Дашборд» — карточки показателей, топ-5 рекомендаций для каждого клиента, графики.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Написано «локальная копия» — нет интернета, взяли последнюю сохранённую выгрузку.</t>
+          <t xml:space="preserve">  • «Рекомендации» — полный список монет с обоснованием каждой.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Красная плашка на дашборде — критичные ошибки данных, лист «Качество данных».</t>
+          <t xml:space="preserve">  • «Профили клиентов» — кто что коллекционирует и какой бюджетный коридор.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
+          <t xml:space="preserve">  • «Каталог монет» — все монеты; у доступных указана оценка цены по аналогам.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • «Качество данных» — 30 автоматических проверок; строки FAIL надо закрыть.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • «Метрики» — насколько точно система угадывала реальные покупки на истории.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="8" customHeight="1">
+      <c r="A23" s="17" t="inlineStr"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>ЕСЛИ ЧТО-ТО НЕ ТАК</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Написано «локальная копия» — нет интернета, взяли последнюю сохранённую выгрузку.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Красная плашка на дашборде — критичные ошибки данных, лист «Качество данных».</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">  • Не открылся файл — он открыт в другом окне Excel, закройте и повторите обновление.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1">
-      <c r="A21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+    <row r="28" ht="8" customHeight="1">
+      <c r="A28" s="17" t="inlineStr"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Подробности расчёта: README.md, docs/Методика.md.</t>
         </is>
